--- a/data/trans_dic/P3A$personadelacasa-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P3A$personadelacasa-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos otra persona se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona del hogar se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,6; 24,17</t>
+          <t>15,93; 23,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,3; 26,9</t>
+          <t>19,48; 26,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,53; 23,91</t>
+          <t>18,27; 23,72</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,03; 30,46</t>
+          <t>21,09; 30,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,08; 25,86</t>
+          <t>17,86; 25,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,86; 27,43</t>
+          <t>21,02; 27,27</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,74; 21,7</t>
+          <t>5,33; 22,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,68; 28,24</t>
+          <t>16,27; 27,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,12; 21,99</t>
+          <t>7,02; 21,79</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,02; 26,48</t>
+          <t>20,08; 26,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,95; 27,84</t>
+          <t>12,6; 28,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,85; 25,51</t>
+          <t>15,45; 25,76</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,2; 34,9</t>
+          <t>24,8; 34,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,71; 20,19</t>
+          <t>12,86; 20,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,22; 24,23</t>
+          <t>17,41; 24,15</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>68,07; 85,94</t>
+          <t>68,42; 85,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,35; 35,58</t>
+          <t>28,85; 36,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39,52; 47,19</t>
+          <t>39,46; 46,91</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19,66; 28,65</t>
+          <t>19,02; 28,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,76; 24,79</t>
+          <t>19,19; 25,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20,41; 26,15</t>
+          <t>20,98; 26,11</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos otra persona se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona del hogar se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>78812; 122121</t>
+          <t>80472; 120302</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>86215; 120180</t>
+          <t>87018; 117620</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>176446; 227596</t>
+          <t>173927; 225831</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>94981; 137588</t>
+          <t>95259; 137476</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>69180; 98937</t>
+          <t>68340; 98233</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>174075; 228895</t>
+          <t>175409; 227521</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31688; 145030</t>
+          <t>35637; 147620</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27746; 46968</t>
+          <t>27068; 46115</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51053; 183555</t>
+          <t>58610; 181840</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>207212; 273970</t>
+          <t>207804; 276076</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>107057; 272263</t>
+          <t>123209; 274137</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>319070; 513431</t>
+          <t>311024; 518608</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>119715; 165775</t>
+          <t>117800; 163903</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>106902; 169905</t>
+          <t>108190; 168805</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>226726; 319019</t>
+          <t>229222; 317858</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>163724; 206697</t>
+          <t>164563; 206611</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>215813; 270884</t>
+          <t>219623; 275827</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>395970; 472738</t>
+          <t>395350; 470003</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>663513; 966976</t>
+          <t>641915; 959267</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>671015; 886779</t>
+          <t>686353; 897324</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1418704; 1817765</t>
+          <t>1458595; 1815130</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$personadelacasa-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P3A$personadelacasa-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,29%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,93; 23,81</t>
+          <t>15,57; 22,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,48; 26,33</t>
+          <t>19,05; 25,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,27; 23,72</t>
+          <t>18,03; 23,19</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,25%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,09; 30,43</t>
+          <t>21,18; 30,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,86; 25,68</t>
+          <t>17,59; 24,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,02; 27,27</t>
+          <t>20,45; 26,4</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,33; 22,09</t>
+          <t>17,44; 25,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,27; 27,72</t>
+          <t>16,78; 28,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,02; 21,79</t>
+          <t>18,23; 24,85</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,08; 26,68</t>
+          <t>20,2; 26,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,6; 28,03</t>
+          <t>24,07; 29,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,45; 25,76</t>
+          <t>22,79; 26,96</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,8; 34,5</t>
+          <t>23,73; 31,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,86; 20,06</t>
+          <t>17,53; 22,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,41; 24,15</t>
+          <t>20,76; 25,37</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>68,42; 85,91</t>
+          <t>69,91; 85,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,85; 36,23</t>
+          <t>28,42; 35,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39,46; 46,91</t>
+          <t>38,69; 46,16</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>25,94%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19,02; 28,42</t>
+          <t>25,3; 28,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19,19; 25,09</t>
+          <t>23,56; 26,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20,98; 26,11</t>
+          <t>24,81; 27,15</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>97633</t>
+          <t>103157</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>100822</t>
+          <t>107547</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>198455</t>
+          <t>210704</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>80472; 120302</t>
+          <t>85711; 125799</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>87018; 117620</t>
+          <t>92903; 126614</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>173927; 225831</t>
+          <t>187236; 240769</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>114817</t>
+          <t>122001</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>82999</t>
+          <t>88631</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>197816</t>
+          <t>210632</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>95259; 137476</t>
+          <t>102246; 145330</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>68340; 98233</t>
+          <t>74431; 104860</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>175409; 227521</t>
+          <t>185295; 239107</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>88029</t>
+          <t>100342</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35717</t>
+          <t>40447</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>123745</t>
+          <t>140789</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>35637; 147620</t>
+          <t>82251; 118571</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27068; 46115</t>
+          <t>31366; 52630</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>58610; 181840</t>
+          <t>120063; 163620</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>238937</t>
+          <t>262851</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>208196</t>
+          <t>230091</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>447133</t>
+          <t>492942</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>207804; 276076</t>
+          <t>228626; 296305</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>123209; 274137</t>
+          <t>207331; 254227</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>311024; 518608</t>
+          <t>454211; 537370</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>139360</t>
+          <t>157031</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>143939</t>
+          <t>165793</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>283299</t>
+          <t>322825</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>117800; 163903</t>
+          <t>134767; 181140</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>108190; 168805</t>
+          <t>145674; 185752</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>229222; 317858</t>
+          <t>290328; 354843</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>189514</t>
+          <t>186853</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>242859</t>
+          <t>270901</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>432374</t>
+          <t>457754</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>164563; 206611</t>
+          <t>165855; 203501</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>219623; 275827</t>
+          <t>239933; 300933</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>395350; 470003</t>
+          <t>418398; 499234</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>868289</t>
+          <t>932236</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>814532</t>
+          <t>903410</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1682821</t>
+          <t>1835645</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>641915; 959267</t>
+          <t>870752; 996962</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>686353; 897324</t>
+          <t>856049; 958432</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1458595; 1815130</t>
+          <t>1755575; 1921141</t>
         </is>
       </c>
     </row>
